--- a/daily_matches/job_matches_2026-03-18.xlsx
+++ b/daily_matches/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Scientist - Modeling and Analytics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>AAA Life Insurance Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Synapse, Data Lake, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,252 +496,217 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5ffe3e0696e29a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2b77322b9e1a41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>come and see</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, XGBoost, LightGBM, Docker, Kubernetes, Git, Snowflake, Tableau, Python</t>
+          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfe211c3ab79af3</t>
+          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ML Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ncontracts</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Copilot, BigQuery, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4fc9074f486fdc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8752763e6582011</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>MLOps Engineer - Senior Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64947efb2ec3dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=d827e60df0032828</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - AI Platforms</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586d05c6f70baaa1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb84733b58c2b5b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Responsible AI</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=832b6dc32fa4dd47</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4b0d633b20148b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Systems and Network Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>System Automation</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CI/CD, Git, NoSQL, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2297f51aadcda9dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Application Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Larson Financial Group</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AKS, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=037be576763d4360</t>
+          <t>https://www.indeed.com/viewjob?jk=368ba395566c62e9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-18.xlsx
+++ b/daily_matches/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Modeling and Analytics</t>
+          <t>Sr Product Mgr II - Content Viewership Data</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAA Life Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Databricks, Tableau, Power BI</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Kafka, Hadoop, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2b77322b9e1a41</t>
+          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41aec199d60a57ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1a69ca785368e7f4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ML Architect</t>
+          <t>Mainframe Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Techmorgonite Software Solutions LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, BigQuery, Git, BigQuery, Python, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8752763e6582011</t>
+          <t>https://www.indeed.com/viewjob?jk=82ad00171a071d4c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps Engineer - Senior Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
+          <t>Redshift, Git, Snowflake, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d827e60df0032828</t>
+          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Platforms</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kissimmee, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, XGBoost, LightGBM, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,77 +636,497 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb84733b58c2b5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=48f4891dd9237660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4b0d633b20148b</t>
+          <t>https://www.indeed.com/viewjob?jk=07699b2a69b9f2ec</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Systems and Network Automation Engineer</t>
+          <t>ML/AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wecom Fiber</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, FastAPI, Git, PostgreSQL, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=299b519ebfb641f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Perfect Path, LLC, d/b/a Trajector Services</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67d38af253bd7067</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer(AI Engineer)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CloudRay Inc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe5af0c262d23015</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kafka Event Orchestration Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Snowflake, Kafka, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33437c8679ef7aee</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Docker MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5572ced1012ba8c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1803a4d8f9691370</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Docker MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=178cdec3ff53ed97</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Platform Architect</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1df0675b818423c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gartner</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Glue, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer - Agentic AI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=368ba395566c62e9</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=765bd089cd60b24a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SR SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dollar General</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Goodlettsville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IXIS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-18.xlsx
+++ b/daily_matches/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Product Mgr II - Content Viewership Data</t>
+          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Kafka, Hadoop, MySQL, MongoDB, Tableau</t>
+          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0de1bf162fb5345</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Docker</t>
+          <t>RAG, FastAPI, CI/CD, Databricks, Kafka, MySQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a69ca785368e7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mainframe Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Techmorgonite Software Solutions LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RAG, Copilot, S3, Kubernetes, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ad00171a071d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, Git, Snowflake, Redshift, Kafka, Hadoop, MySQL, Cassandra, NoSQL, Python</t>
+          <t>Kinesis, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52a3cc4b9e4c96e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Backend Engineer (FastAPI + Azure DevOps + Clerk)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>SERVANT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kissimmee, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL</t>
+          <t>FastAPI, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f4891dd9237660</t>
+          <t>https://www.indeed.com/viewjob?jk=cf0780a6b55e3bcc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Scientist / Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Shift Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Databricks</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, MLflow, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07699b2a69b9f2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=af9c79e11a78c858</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ML/AI Engineer</t>
+          <t>AI Engineer (Human-Led AI Orchestration + Action Points)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>SERVANT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, FastAPI, Git, PostgreSQL, MySQL, Python</t>
+          <t>AI Engineer, Prompt Engineering, FastAPI, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,427 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299b519ebfb641f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Perfect Path, LLC, d/b/a Trajector Services</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Kubernetes, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67d38af253bd7067</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer(AI Engineer)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CloudRay Inc</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Pinecone, FastAPI, Docker, Kubernetes, Git, NoSQL, Python</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5af0c262d23015</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Kafka Event Orchestration Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Snowflake, Kafka, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33437c8679ef7aee</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Docker MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5572ced1012ba8c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1803a4d8f9691370</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Docker MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=178cdec3ff53ed97</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Platform Architect</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1df0675b818423c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer (Python, ETL) - Master Data Management (MDM)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Gartner</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Glue, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ceeabf66fcba285d</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior AI Software Engineer - Agentic AI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Citizens</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Johnston, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=765bd089cd60b24a</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dollar General</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Goodlettsville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Git, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87178150b06d3f51</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>IXIS</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b5e1124148b1b77</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55f5b2c9d63429a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d08f6c69c7f8354</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-18.xlsx
+++ b/daily_matches/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multi-Cloud SQL/Oracle Database Administrator (DBA)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL, NoSQL, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, Azure ML, Synapse, Data Lake, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2c1b2c3f27c3043</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ac8b2469720423</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, Databricks, Kafka, MySQL, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec14b3c9bfc49d5</t>
+          <t>https://www.indeed.com/viewjob?jk=817982b1dba07e3b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer (Data Scientist)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, GitHub Actions, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1446a6003c62f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d771bf42de224ba7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kinesis, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de9c257b395e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d18c7217c63ba8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Engineer (FastAPI + Azure DevOps + Clerk)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SERVANT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, S3, FastAPI, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0780a6b55e3bcc</t>
+          <t>https://www.indeed.com/viewjob?jk=58fb92720cd393bb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist / Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shift Technology</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, MLflow, Databricks, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,392 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af9c79e11a78c858</t>
+          <t>https://www.indeed.com/viewjob?jk=771a15dfe2c6152a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer (Human-Led AI Orchestration + Action Points)</t>
+          <t>Full Stack NextJS Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ba0e3963acb9e99</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c4867aa3e39c299</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DevOps &amp; Cloud Engineer (Azure + Backend Enablement)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>SERVANT</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f72937fa5cc11feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Software Engineering PhD Intern</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61a4a259d757b00c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Prompt Engineering, FastAPI, CI/CD, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d08f6c69c7f8354</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c54015bef73b1d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TRUITY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0920cf73e7393683</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TRUITY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27bd43325620dab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TRUITY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lawrence, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76a500cb351b4eae</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRUITY CREDIT UNION</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bartlesville, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e76c1fe80d7c3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf896a64f84f691e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-18.xlsx
+++ b/daily_matches/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, Azure ML, Synapse, Data Lake, MLflow, CI/CD</t>
+          <t>AI Engineer, Generative AI, RAG, S3, EC2, FastAPI, AKS, Git, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ac8b2469720423</t>
+          <t>https://www.indeed.com/viewjob?jk=34aeea1e0d978ae5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Aegis Mobile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Azure ML, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817982b1dba07e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1b0da765859d0c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer (Data Scientist)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d771bf42de224ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=9a9288e20d488b04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Solutions/Presales Engineer - FED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bigid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
+          <t>RAG, S3, Redshift, Docker, Kubernetes, Redshift, Hadoop, MongoDB, Cassandra, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d18c7217c63ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=25c925dfb10d9334</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, FastAPI, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Pinecone, Data Lake, Kinesis, Snowflake, Databricks, Kafka, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fb92720cd393bb</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer | Xbox Advertising</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Activision</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
+          <t>RAG, Data Lake, Kafka, MySQL, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=771a15dfe2c6152a</t>
+          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack NextJS Developer</t>
+          <t>Senior Software Engineer - 3P Partnerships</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>RAG, BigQuery, GitHub Actions, Terraform, Git, Snowflake, BigQuery, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba0e3963acb9e99</t>
+          <t>https://www.indeed.com/viewjob?jk=8269d8d544b9b802</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Software Engineer - 3P Partnerships</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gopuff</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+          <t>RAG, BigQuery, GitHub Actions, Terraform, Git, Snowflake, BigQuery, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4867aa3e39c299</t>
+          <t>https://www.indeed.com/viewjob?jk=9c14cad936f5cb6d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps &amp; Cloud Engineer (Azure + Backend Enablement)</t>
+          <t>Artificial Intelligence (AI) Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SERVANT</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, CI/CD, Databricks, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72937fa5cc11feb</t>
+          <t>https://www.indeed.com/viewjob?jk=e0316a0532c08e93</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Software Engineering PhD Intern</t>
+          <t>Software Engineer (Node.js, Python, Go, Azure)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, OpenCV, Docker, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a4a259d757b00c</t>
+          <t>https://www.indeed.com/viewjob?jk=886b7d91a82c27b0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - Remote</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ServiceUp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, BigQuery, BigQuery, PostgreSQL, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c54015bef73b1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0035af3a6d96e50f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer (ETL)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TRUITY CREDIT UNION</t>
+          <t>Radial</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
+          <t>EC2, Glue, Snowflake, Hadoop, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0920cf73e7393683</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer - Development and Product Support (Work Location: In-Office schedule: in Alpharetta, GA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TRUITY CREDIT UNION</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
+          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bd43325620dab4</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4789fa1d3341</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>AI Data Strategist - Customer Success</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TRUITY CREDIT UNION</t>
+          <t>Toast, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lawrence, KS, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
+          <t>Gemini, Cortex, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,112 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a500cb351b4eae</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TRUITY CREDIT UNION</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bartlesville, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Prompt Engineering, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e76c1fe80d7c3019</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf896a64f84f691e</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b75a7809930220b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9ef1125749f5e7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-18.xlsx
+++ b/daily_matches/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Artificial Intelligence &amp; Machine Learning Engineer, Associate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, S3, EC2, FastAPI, AKS, Git, PostgreSQL, NoSQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Copilot, FAISS, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34aeea1e0d978ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f0e9eb9da3b6fb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aegis Mobile</t>
+          <t>OnMed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Azure ML, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1b0da765859d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e544feca7de01ac</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Git, PySpark, Polars, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9288e20d488b04</t>
+          <t>https://www.indeed.com/viewjob?jk=e565f8d230a674d3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solutions/Presales Engineer - FED</t>
+          <t>Scientist, Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bigid</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Docker, Kubernetes, Redshift, Hadoop, MongoDB, Cassandra, SQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c925dfb10d9334</t>
+          <t>https://www.indeed.com/viewjob?jk=3294237f84426c30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Data Lake, Kinesis, Snowflake, Databricks, Kafka, MongoDB, SQL, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7bed78bd5d257f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4f32faeb712f204</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | Xbox Advertising</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Activision</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kafka, MySQL, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfb862649ecf3ff</t>
+          <t>https://www.indeed.com/viewjob?jk=295590b7c539fa4d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 3P Partnerships</t>
+          <t>IAM Database Intelligence Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, GitHub Actions, Terraform, Git, Snowflake, BigQuery, SQL, R, Java</t>
+          <t>RAG, S3, Docker, Kubernetes, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8269d8d544b9b802</t>
+          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 3P Partnerships</t>
+          <t>Software Development Engineer 2 - Front-End</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gopuff</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, GitHub Actions, Terraform, Git, Snowflake, BigQuery, SQL, R, Java</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c14cad936f5cb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) Engineer II</t>
+          <t>Senior Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, CI/CD, Databricks, Python, R, Java, Optimization</t>
+          <t>RAG, S3, Data Lake, Kinesis, Docker, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0316a0532c08e93</t>
+          <t>https://www.indeed.com/viewjob?jk=8c87fe3f873334f0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (Node.js, Python, Go, Azure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886b7d91a82c27b0</t>
+          <t>https://www.indeed.com/viewjob?jk=808b7df8ef059314</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ServiceUp</t>
+          <t>Cross River Bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lee, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, BigQuery, PostgreSQL, Python, SQL, R, A/B Testing</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0035af3a6d96e50f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b20af56ac8176a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer (ETL)</t>
+          <t>Research Software and AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Radial</t>
+          <t>University of North Carolina at Chapel Hill</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Chapel Hill, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EC2, Glue, Snowflake, Hadoop, NoSQL, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, FastAPI, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,77 +881,252 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0a9c4efd739d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d73e519d3170a57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Development and Product Support (Work Location: In-Office schedule: in Alpharetta, GA)</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>RaYnmaker Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Pinecone, Kinesis, Docker, Kubernetes, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4789fa1d3341</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ab7bd8fafcacd1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Data Strategist - Customer Success</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Toast, Inc</t>
+          <t>RaYnmaker Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Kinesis, Docker, Kubernetes, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c41ff1fec3a36a16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RaYnmaker Inc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Kinesis, Docker, Kubernetes, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf109bcb38595442</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Automation Engineer (Mid level SDET)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Medrio</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2f89f6db54cefa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Clarip</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Falls Church, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docker, Hadoop, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf476a068c6d68fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74454b5ae0866fa3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alarm.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Boston, MA, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D20" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Gemini, Cortex, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9ef1125749f5e7</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=244ce1bcd7a3c188</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-18.xlsx
+++ b/daily_matches/job_matches_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Machine Learning Engineer, Associate</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Copilot, FAISS, Prompt Engineering, Docker, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f0e9eb9da3b6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3972759b3173959f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e544feca7de01ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c1885d139b3f38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Machine Learning</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Git, PySpark, Polars, Power BI</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e565f8d230a674d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c70566192b1dea40</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Scientist, Data</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, CI/CD, Databricks, Python</t>
+          <t>RAG, S3, EC2, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3294237f84426c30</t>
+          <t>https://www.indeed.com/viewjob?jk=008b82df0092f214</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,46 +622,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>PyTorch, XGBoost, Azure ML, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f32faeb712f204</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f58c5c3f56232c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, AWS SageMaker, S3, Glue, Athena, Redshift, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295590b7c539fa4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8020b3571a5d8bac</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IAM Database Intelligence Engineer</t>
+          <t>SAP Data Migration Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Glue, Redshift, BigQuery, Synapse, Kinesis, Snowflake, Databricks, BigQuery, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8161b23e8c863c</t>
+          <t>https://www.indeed.com/viewjob?jk=c6ffedc59232b1e6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2 - Front-End</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Snowflake, Redshift, Tableau, Power BI, Quicksight</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5b6a2b2181861f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9d157dc8fc2762</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Fullstack</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Kinesis, Docker, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>RAG, Copilot, Azure ML, BigQuery, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c87fe3f873334f0</t>
+          <t>https://www.indeed.com/viewjob?jk=df6a52b151ef3475</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Agentic AI Developer (Entry-Level)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808b7df8ef059314</t>
+          <t>https://www.indeed.com/viewjob?jk=29fa6bc00387a128</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cross River Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Lee, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b20af56ac8176a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2f9e5ffecfd57f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Research Software and AI Engineer</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of North Carolina at Chapel Hill</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chapel Hill, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, FastAPI, CI/CD, Git, Databricks, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d73e519d3170a57</t>
+          <t>https://www.indeed.com/viewjob?jk=2caded056cbeda86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RaYnmaker Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Kinesis, Docker, Kubernetes, Kafka, Python, R, Scala</t>
+          <t>LangChain, Hugging Face, Docker, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ab7bd8fafcacd1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b43aaa6eb3f6bed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>AWS &amp; Databricks Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RaYnmaker Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Kinesis, Docker, Kubernetes, Kafka, Python, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Terraform, Git, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c41ff1fec3a36a16</t>
+          <t>https://www.indeed.com/viewjob?jk=cd84bf5f05e0bb19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RaYnmaker Inc</t>
+          <t>Claritas Rx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,77 +976,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Kinesis, Docker, Kubernetes, Kafka, Python, R, Scala</t>
+          <t>RAG, S3, EC2, GitHub Actions, Terraform, Git, PostgreSQL, Tableau, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf109bcb38595442</t>
+          <t>https://www.indeed.com/viewjob?jk=5f338463dc36bfb7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Automation Engineer (Mid level SDET)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Medrio</t>
+          <t>Veho</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2f89f6db54cefa</t>
+          <t>https://www.indeed.com/viewjob?jk=b95b48d5f5ed9b2f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clarip</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Hadoop, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf476a068c6d68fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf88dd29a168239</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Python, SQL, R, Scala, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74454b5ae0866fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6c561ab31257ac</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Database Support Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, SQL, R</t>
+          <t>RAG, S3, EC2, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,182 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244ce1bcd7a3c188</t>
+          <t>https://www.indeed.com/viewjob?jk=084fd6d736daf8f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AWS Developer / Administrator</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ESYSTEMS, INC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d8e2e16286c1be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Partner Experience</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Upstart</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Git, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65041e162ee4050f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineering Co-Op, Summer-Winter 2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Edwards Lifesciences</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Alton, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, AWS SageMaker, CI/CD, Terraform, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f14a0a81f3739da</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, XGBoost, PySpark, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc0cd89bd8f12691</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer, Commercial Banking</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=920404beb4ef2ee0</t>
         </is>
       </c>
     </row>
